--- a/public/project-atlas/Project_Atlas_Model_Starter.xlsx
+++ b/public/project-atlas/Project_Atlas_Model_Starter.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="202">
   <si>
     <t>PROJECT ATLAS</t>
   </si>
@@ -92,7 +92,7 @@
     <t>Version du cas</t>
   </si>
   <si>
-    <t>project_atlas_v1 · 1.0.0</t>
+    <t>project_atlas_v1 · 1.1.0</t>
   </si>
   <si>
     <t>CONVENTIONS</t>
@@ -428,6 +428,12 @@
     <t>= Prix par action implicite (€)</t>
   </si>
   <si>
+    <t>Prix implicite au 1er quartile (€)</t>
+  </si>
+  <si>
+    <t>Prix implicite au 3e quartile (€)</t>
+  </si>
+  <si>
     <t>Rappel : un comparable peut sembler décoté pour de bonnes raisons. Regarde la croissance et la marge avant de conclure.</t>
   </si>
   <si>
@@ -524,7 +530,7 @@
     <t>WACC ↓  /  croissance à l'infini →</t>
   </si>
   <si>
-    <t>La table de sensibilité se construit avec Données → Analyse de scénarios → Table de données (cellule d'entrée ligne = g, colonne = WACC).</t>
+    <t>Sélectionne C54:H59 puis Données → Analyse de scénarios → Table de données. Cellule d'entrée en ligne : D17 (croissance). Cellule d'entrée en colonne : D16 (WACC). La cellule C54 référence déjà la sortie à sensibiliser.</t>
   </si>
   <si>
     <t>SYNTHÈSE DE VALORISATION</t>
@@ -620,13 +626,13 @@
     <t>case_version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>grader_version</t>
   </si>
   <si>
-    <t>1.0</t>
+    <t>1.1</t>
   </si>
   <si>
     <t>variant</t>
@@ -783,7 +789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -823,14 +829,15 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="169" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="171" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2259,7 +2266,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J34"/>
+  <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -2546,9 +2553,21 @@
       </c>
       <c r="D31" s="26"/>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="8" t="s">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
         <v>129</v>
+      </c>
+      <c r="D32" s="27"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="27"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="8" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2568,48 +2587,48 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D7" s="27">
+        <v>135</v>
+      </c>
+      <c r="D7" s="28">
         <v>0.032</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" s="27">
+        <v>136</v>
+      </c>
+      <c r="D8" s="28">
         <v>0.065</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="28">
+        <v>137</v>
+      </c>
+      <c r="D9" s="29">
         <v>1.12</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D10" s="27">
+        <v>138</v>
+      </c>
+      <c r="D10" s="28">
         <v>0.05</v>
       </c>
     </row>
@@ -2623,7 +2642,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D12" s="19">
         <v>0.3</v>
@@ -2631,7 +2650,7 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D13" s="19">
         <v>0.7</v>
@@ -2639,27 +2658,27 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D15" s="29"/>
+        <v>141</v>
+      </c>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D16" s="29"/>
+        <v>142</v>
+      </c>
+      <c r="D16" s="30"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" s="27">
+        <v>143</v>
+      </c>
+      <c r="D17" s="28">
         <v>0.025</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
@@ -2711,11 +2730,11 @@
       <c r="B23" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
@@ -2746,15 +2765,15 @@
       <c r="B25" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D26" s="24">
         <f>Atlas_Raw!F10</f>
@@ -2789,7 +2808,7 @@
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D28" s="21"/>
       <c r="E28" s="21"/>
@@ -2799,7 +2818,7 @@
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D29" s="21"/>
       <c r="E29" s="21"/>
@@ -2809,7 +2828,7 @@
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="25"/>
@@ -2819,7 +2838,7 @@
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D31" s="24">
         <f>D26</f>
@@ -2844,7 +2863,7 @@
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D32" s="24">
         <f>-Atlas_Raw!F12</f>
@@ -2869,7 +2888,7 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D33" s="24">
         <f>-Atlas_Raw!F13</f>
@@ -2894,37 +2913,37 @@
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D34" s="31">
+        <v>152</v>
+      </c>
+      <c r="D34" s="32">
         <v>0.5</v>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="32">
         <v>1.5</v>
       </c>
-      <c r="F34" s="31">
+      <c r="F34" s="32">
         <v>2.5</v>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="32">
         <v>3.5</v>
       </c>
-      <c r="H34" s="31">
+      <c r="H34" s="32">
         <v>4.5</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
+        <v>153</v>
+      </c>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
@@ -2934,24 +2953,24 @@
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D40" s="21"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D41" s="21"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D42" s="25"/>
     </row>
@@ -2993,7 +3012,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D47" s="25"/>
     </row>
@@ -3008,90 +3027,94 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D49" s="26"/>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C53" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D54" s="33">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="54" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C54" s="34">
+        <f>D49</f>
+        <v>28.746475549162376</v>
+      </c>
+      <c r="D54" s="35">
         <v>0.015</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="35">
         <v>0.02</v>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="35">
         <v>0.025</v>
       </c>
-      <c r="G54" s="33">
+      <c r="G54" s="35">
         <v>0.03</v>
       </c>
-      <c r="H54" s="33">
+      <c r="H54" s="35">
         <v>0.035</v>
       </c>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C55" s="33">
+      <c r="C55" s="35">
         <v>0.075</v>
       </c>
-      <c r="D55" s="34"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="34"/>
-      <c r="H55" s="34"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="27"/>
     </row>
     <row r="56" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C56" s="33">
+      <c r="C56" s="35">
         <v>0.08</v>
       </c>
-      <c r="D56" s="34"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="34"/>
-      <c r="H56" s="34"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C57" s="33">
+      <c r="C57" s="35">
         <v>0.085</v>
       </c>
-      <c r="D57" s="34"/>
-      <c r="E57" s="34"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="34"/>
-      <c r="H57" s="34"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C58" s="33">
+      <c r="C58" s="35">
         <v>0.09</v>
       </c>
-      <c r="D58" s="34"/>
-      <c r="E58" s="34"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="34"/>
-      <c r="H58" s="34"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
     </row>
     <row r="59" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C59" s="33">
+      <c r="C59" s="35">
         <v>0.095</v>
       </c>
-      <c r="D59" s="34"/>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="34"/>
-      <c r="H59" s="34"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -3105,65 +3128,65 @@
   <dimension ref="B2:E14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
+        <v>170</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
+        <v>171</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C10" s="26"/>
       <c r="E10" s="26"/>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="35" t="s">
-        <v>171</v>
+      <c r="B13" s="36" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="36" t="s">
-        <v>172</v>
+      <c r="B14" s="37" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -3184,119 +3207,119 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D6" s="38"/>
+        <v>179</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="39"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D7" s="38"/>
+        <v>181</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" s="39"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="38"/>
+      <c r="D8" s="39"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="38"/>
+        <v>183</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="39"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D10" s="38"/>
+        <v>184</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="39"/>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D11" s="38"/>
+        <v>185</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="39"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D12" s="38"/>
+        <v>186</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="39"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D13" s="38"/>
+        <v>187</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="39"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D14" s="38"/>
+        <v>188</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="39"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D15" s="38"/>
+        <v>189</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D15" s="39"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="39" t="s">
-        <v>188</v>
-      </c>
-      <c r="D18" s="40"/>
+      <c r="B18" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" s="41"/>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -3312,42 +3335,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/public/project-atlas/Project_Atlas_Model_Starter.xlsx
+++ b/public/project-atlas/Project_Atlas_Model_Starter.xlsx
@@ -632,7 +632,7 @@
     <t>grader_version</t>
   </si>
   <si>
-    <t>1.1</t>
+    <t>1.2</t>
   </si>
   <si>
     <t>variant</t>
